--- a/Baseline Data Use Case Alignment - Offers V1.xlsx
+++ b/Baseline Data Use Case Alignment - Offers V1.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V301"/>
+  <dimension ref="A1:V342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.73046875" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
@@ -25109,6 +25109,3161 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Eloqua Record ID</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>What is the Eloqua record identifier for this form submission?</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>System-generated Eloqua record identifier assigned at form submission.</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Provides the durable submission identifier for auditability, deduplication, and downstream integrations.</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Date Submitted</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>When was this form submission received?</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>System timestamp captured at form submission.</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Date/Time</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Supports submission timing, SLA monitoring, and operational reporting.</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Cisco ID Account Creation Opt-In</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Does the contact want to create a free Cisco ID account?</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Customer Input</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Optional checkbox selected by the customer during form submission.</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Captures account-creation intent for onboarding, follow-up routing, and experience personalization.</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Preferred Language</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>What is the contact's preferred language?</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Customer Input</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Optional customer-selected language preference captured on the form.</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Picklist/Text</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Supports localized follow-up, routing, and customer experience personalization.</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Enquiry Type</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>What type of enquiry is the contact submitting?</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Customer Input</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Required customer-selected enquiry category captured on the Contact Us form.</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Picklist</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Classifies the contact's intent for routing, lead scoring, seller enablement, and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>IRM Enquiry 2</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>What is the secondary IRM enquiry classification?</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Customer Input</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Optional secondary enquiry classification field captured on the Contact Us form.</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Picklist/Text</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Provides supplemental enquiry classification for routing, scoring, and follow-up context.</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Additional Enquiry Details</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>What additional details did the contact provide about their enquiry?</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Customer Input</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Optional free-text response captured from the customer on the Contact Us form.</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Provides qualitative enquiry context for seller enablement and operational review.</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Contact Request</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Did the contact request follow-up?</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>System-defaulted or derived contact-request flag for Contact Us submissions.</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Indicates follow-up intent for routing, seller enablement, and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>ELQ Site ID</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>What is the Eloqua site identifier for this submission?</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>System-captured Eloqua site identifier associated with the form submission.</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Supports site-level operational reporting, validation, and downstream integrations.</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>System Updated By</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Which system process last updated this record?</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>System-captured process name indicating how the record was created or updated.</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Supports auditability and operational validation of submission source.</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ELQ Form ID</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>What is the Eloqua form identifier for this submission?</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>System-captured Eloqua form identifier for the Contact Us form.</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Connects the submission to the source form for operational reporting and validation.</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>ELQ Landing Page ID</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>What is the Eloqua landing page identifier for this submission?</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>System-captured Eloqua landing page identifier associated with the submission.</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Connects the submission to the originating landing page for attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Form Submit Date</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>What is the form submit date captured by the system?</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>System-captured form submission date passed from Eloqua or Tealium.</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Date/Time</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Supports submission timing analysis and operational reporting.</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Landing Page ID/URL</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>What landing page did the contact submit the form from?</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Captured from the landing page URL or ID at form submission and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Captures landing page context for attribution, operational reporting, and seller enablement.</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>What is the submission sub-category?</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>System-assigned sub-category for Contact Us submissions (e.g., Call ASAP).</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Supports urgency-based routing, lead scoring, and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Org Source</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>What is the organizational source for this submission?</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>System-assigned organizational source (e.g., Marketing, CX, IOT) for the submission.</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Supports source-based routing, attribution alignment, and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Contact Flag</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>What is the contact requirement flag for this submission?</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>System-assigned flag indicating contact requirement status for the submission.</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Supports routing validation and operational reporting.</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Common Campaign ID</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>What is the common campaign identifier for this submission?</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Captured from campaign tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Connects the submission to campaign taxonomy for attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Eloqua Campaign ID</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>What is the Eloqua campaign identifier for this submission?</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>System-captured Eloqua campaign identifier associated with the form submission.</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Connects the submission to Eloqua campaign reporting and attribution analysis.</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>What is the event identifier associated with this submission?</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Captured from event tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Connects the submission to event-based attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>What is the form language/locale for this submission?</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>System-captured locale code (e.g., en_us, ja_jp) for the form submission.</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Supports localized operational reporting, routing, and customer experience alignment.</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Previous Referrer</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>What was the previous referrer URL before form submission?</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Captured by Tealium from the customer's previous referrer and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Supports referrer-based attribution journey analysis and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>CP_GUTC</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>What is the Cisco tracking cookie value for this submission?</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Captured by Tealium tracking cookie and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Supports visitor tracking, identity stitching, and attribution analysis.</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Google Click ID</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>What is the Google click identifier (gclid) for this submission?</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Captured from Google Ads click tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Supports paid search click-level attribution and campaign performance reporting.</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Media Campaign Name</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>What is the media campaign name for this submission?</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Captured from media tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Supports media campaign attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Media Search Keywords</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>What media search keywords are associated with this submission?</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Captured from media search tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Supports keyword-level attribution analysis and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Media Country Site</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>What media country site is associated with this submission?</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Captured from media tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Supports geo-based media attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Media Creative</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>What media creative is associated with this submission?</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Captured from media creative tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Supports creative-level attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Media Position</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>What media position is associated with this submission?</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Captured from media placement tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Supports placement position attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Media Placement</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>What media placement is associated with this submission?</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Captured from media placement tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Supports placement-level attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Media Referring Site</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>What media referring site is associated with this submission?</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Captured from media referrer tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Supports referrer-based media attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Media Unpaid Search</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>What unpaid search media data is associated with this submission?</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Captured from unpaid search media tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Supports organic/unpaid search attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>utm_id</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>What is the UTM ID for this submission?</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Captured by Tealium from the customer's driving URL and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Identifies the campaign ID for future attribution, operational, and funnel reporting.</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Content Asset ID</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>What is the content asset identifier for this submission?</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Captured from content asset tracking parameters and passed to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Connects the submission to content assets for attribution and operational reporting.</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>API Validation Error</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Were any API validation errors captured for this submission?</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>System-captured API validation error message, if any, during form processing.</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Supports operational monitoring, error tracking, and submission quality review.</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Tray Token</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>What is the Tray.io landing page token for this submission?</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool/Tealium</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Captured landing page token passed from Tealium/Tray.io to Marketing Automation Tool.</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Supports landing page validation, orchestration traceability, and operational reporting.</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Redirect to Intersight Login Page</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Was the contact redirected to the Intersight login page?</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>System flag indicating redirect to Intersight login page during form flow.</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Captures login redirect context for routing and follow-up personalization.</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Login Flag</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Was the contact logged in at the time of submission?</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>System-captured flag indicating whether the contact was authenticated at submission.</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Supports identity-aware routing, lead scoring, and seller enablement context.</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>OKTA Response</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>What OKTA authentication response was captured for this submission?</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>System-captured OKTA authentication response during login flow, if applicable.</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Supports authentication validation and operational troubleshooting.</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Contact Source Original</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>What is the original contact source for this submission?</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>System-captured original source identifier (e.g., Eloqua-Form-submit-ContactSales6493).</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Supports source lineage for attribution, operational reporting, and seller enablement.</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Online Forms</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Hand Raiser</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Offers - Contact Us</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Form Submit</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>8 - Additional Activity Information</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Contact Sales</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Did the contact request sales contact?</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Marketing Automation Tool</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>System-captured contact sales flag for the submission.</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Supports sales routing, lead scoring, and seller enablement decisions.</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>Potential</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V206"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
